--- a/p6_deployment/data/germany/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_filled.xlsx
@@ -703,22 +703,22 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>25.93146853146853</v>
+        <v>25.84363636363636</v>
       </c>
       <c r="W2" t="n">
-        <v>184.7412587412588</v>
+        <v>184.6181818181818</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>70.13846153846154</v>
+        <v>70.08363636363637</v>
       </c>
       <c r="Z2" t="n">
-        <v>2324195.804195804</v>
+        <v>2310060.606060606</v>
       </c>
       <c r="AA2" t="n">
-        <v>73.05314685314686</v>
+        <v>73.09454545454545</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -727,22 +727,22 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>26.21577501445923</v>
+        <v>26.32033834586466</v>
       </c>
       <c r="AI2" t="n">
-        <v>185.8954742625795</v>
+        <v>186.0177443609022</v>
       </c>
       <c r="AJ2" t="n">
         <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>66.83335743204164</v>
+        <v>66.88057644110276</v>
       </c>
       <c r="AL2" t="n">
-        <v>1262396.616541354</v>
+        <v>1260743.73433584</v>
       </c>
       <c r="AM2" t="n">
-        <v>71.09064488143436</v>
+        <v>70.93689223057645</v>
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr">
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26.05194805194805</v>
+        <v>25.93048128342246</v>
       </c>
       <c r="Q3" t="n">
-        <v>185.6753246753247</v>
+        <v>185.5828877005348</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>67.1103896103896</v>
+        <v>67.12299465240642</v>
       </c>
       <c r="T3" t="n">
-        <v>1187987.012987013</v>
+        <v>1207620.320855615</v>
       </c>
       <c r="U3" t="n">
-        <v>69.59740259740259</v>
+        <v>69.77540106951871</v>
       </c>
       <c r="V3" t="n">
-        <v>25.90151515151515</v>
+        <v>25.88363636363636</v>
       </c>
       <c r="W3" t="n">
-        <v>183.1590909090909</v>
+        <v>183.4181818181818</v>
       </c>
       <c r="X3" t="n">
-        <v>1.598484848484848</v>
+        <v>1.592727272727272</v>
       </c>
       <c r="Y3" t="n">
-        <v>74.45454545454545</v>
+        <v>74.4290909090909</v>
       </c>
       <c r="Z3" t="n">
-        <v>6766666.666666667</v>
+        <v>6750181.818181817</v>
       </c>
       <c r="AA3" t="n">
-        <v>78.35606060606061</v>
+        <v>78.27272727272728</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.59821428571428</v>
+        <v>24.63643790849673</v>
       </c>
       <c r="AC3" t="n">
-        <v>184.0823412698413</v>
+        <v>184.0024509803922</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>64.85813492063491</v>
+        <v>64.77205882352941</v>
       </c>
       <c r="AF3" t="n">
-        <v>977405.753968254</v>
+        <v>957536.7647058824</v>
       </c>
       <c r="AG3" t="n">
-        <v>68.78769841269842</v>
+        <v>68.62254901960785</v>
       </c>
       <c r="AH3" t="n">
-        <v>25.84755291005291</v>
+        <v>26.10392546583851</v>
       </c>
       <c r="AI3" t="n">
-        <v>184.9790013227513</v>
+        <v>184.7884375431332</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.465608465608466</v>
+        <v>1.496536231884058</v>
       </c>
       <c r="AK3" t="n">
-        <v>71.76984126984127</v>
+        <v>72.19923188405797</v>
       </c>
       <c r="AL3" t="n">
-        <v>4261069.775132275</v>
+        <v>4507439.320220841</v>
       </c>
       <c r="AM3" t="n">
-        <v>76.27976190476191</v>
+        <v>76.34969082125603</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>26.5530303030303</v>
+        <v>26.43181818181818</v>
       </c>
       <c r="W4" t="n">
-        <v>185.8787878787879</v>
+        <v>185.7916666666667</v>
       </c>
       <c r="X4" t="n">
-        <v>1.795454545454545</v>
+        <v>1.78030303030303</v>
       </c>
       <c r="Y4" t="n">
-        <v>75.31060606060606</v>
+        <v>75.21590909090908</v>
       </c>
       <c r="Z4" t="n">
-        <v>8715151.515151516</v>
+        <v>8631818.181818182</v>
       </c>
       <c r="AA4" t="n">
-        <v>78.81818181818183</v>
+        <v>78.88257575757576</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -993,22 +993,22 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>24.07903439153439</v>
+        <v>24.32393389118932</v>
       </c>
       <c r="AI4" t="n">
-        <v>185.0983796296296</v>
+        <v>184.7463804060272</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.308531746031746</v>
+        <v>1.346938262019783</v>
       </c>
       <c r="AK4" t="n">
-        <v>70.4890873015873</v>
+        <v>70.98909449045318</v>
       </c>
       <c r="AL4" t="n">
-        <v>4545899.470899471</v>
+        <v>4994844.414970095</v>
       </c>
       <c r="AM4" t="n">
-        <v>77.3587962962963</v>
+        <v>77.42874036691971</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr">
@@ -1075,22 +1075,22 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>27.18181818181818</v>
+        <v>27.18560606060606</v>
       </c>
       <c r="W5" t="n">
-        <v>185.0419580419581</v>
+        <v>185.1931818181818</v>
       </c>
       <c r="X5" t="n">
-        <v>3.146853146853147</v>
+        <v>3.143939393939394</v>
       </c>
       <c r="Y5" t="n">
-        <v>82.37762237762239</v>
+        <v>82.46969696969698</v>
       </c>
       <c r="Z5" t="n">
-        <v>44731993.00699301</v>
+        <v>45745265.15151515</v>
       </c>
       <c r="AA5" t="n">
-        <v>84.96503496503496</v>
+        <v>84.97727272727273</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1099,22 +1099,22 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>24.63843101343101</v>
+        <v>24.87941074758151</v>
       </c>
       <c r="AI5" t="n">
-        <v>182.2466422466422</v>
+        <v>182.0659746643728</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.005494505494505</v>
+        <v>2.147727117943079</v>
       </c>
       <c r="AK5" t="n">
-        <v>77.13530219780219</v>
+        <v>77.91587622678512</v>
       </c>
       <c r="AL5" t="n">
-        <v>23187456.12026862</v>
+        <v>26298143.27481081</v>
       </c>
       <c r="AM5" t="n">
-        <v>82.6941391941392</v>
+        <v>83.04825326725356</v>
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
@@ -1192,22 +1192,22 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>24.97855477855478</v>
+        <v>24.84925252525252</v>
       </c>
       <c r="W6" t="n">
-        <v>184.7278943278943</v>
+        <v>184.8076767676768</v>
       </c>
       <c r="X6" t="n">
-        <v>1.500621600621601</v>
+        <v>1.49220202020202</v>
       </c>
       <c r="Y6" t="n">
-        <v>75.24040404040404</v>
+        <v>75.25357575757576</v>
       </c>
       <c r="Z6" t="n">
-        <v>8566565.656565655</v>
+        <v>8616650.505050505</v>
       </c>
       <c r="AA6" t="n">
-        <v>78.22665112665113</v>
+        <v>78.27482828282828</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1216,22 +1216,22 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>23.23699633699633</v>
+        <v>23.43553056554429</v>
       </c>
       <c r="AI6" t="n">
-        <v>183.7899267399267</v>
+        <v>183.4115297482838</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.277747252747253</v>
+        <v>1.295255403000254</v>
       </c>
       <c r="AK6" t="n">
-        <v>72.41016483516484</v>
+        <v>72.71196026297628</v>
       </c>
       <c r="AL6" t="n">
-        <v>6047248.168498168</v>
+        <v>6241387.857324472</v>
       </c>
       <c r="AM6" t="n">
-        <v>78.27152014652015</v>
+        <v>78.22619705059751</v>
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
@@ -1302,22 +1302,22 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>23.73106060606061</v>
+        <v>23.73030303030303</v>
       </c>
       <c r="W7" t="n">
-        <v>183.1174242424242</v>
+        <v>183.2090909090909</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>69.09393939393938</v>
+        <v>69.14181818181818</v>
       </c>
       <c r="Z7" t="n">
-        <v>2318825.757575757</v>
+        <v>2332030.303030303</v>
       </c>
       <c r="AA7" t="n">
-        <v>75.30000000000001</v>
+        <v>75.36121212121212</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1326,22 +1326,22 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>22.76438492063492</v>
+        <v>22.88650793650794</v>
       </c>
       <c r="AI7" t="n">
-        <v>183.6526124338624</v>
+        <v>183.4554232804233</v>
       </c>
       <c r="AJ7" t="n">
         <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>63.55125661375661</v>
+        <v>63.91600529100528</v>
       </c>
       <c r="AL7" t="n">
-        <v>1168303.571428571</v>
+        <v>1211101.190476191</v>
       </c>
       <c r="AM7" t="n">
-        <v>71.88244047619048</v>
+        <v>71.86428571428571</v>
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr">
@@ -1419,22 +1419,22 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>26.09166666666667</v>
+        <v>26.28</v>
       </c>
       <c r="W8" t="n">
-        <v>186.0333333333333</v>
+        <v>185.8266666666667</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>69.375</v>
+        <v>69.52666666666667</v>
       </c>
       <c r="Z8" t="n">
-        <v>1829166.666666667</v>
+        <v>1836666.666666667</v>
       </c>
       <c r="AA8" t="n">
-        <v>73.58333333333333</v>
+        <v>73.32666666666667</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1443,22 +1443,22 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>25.29220085470086</v>
+        <v>25.59672364672365</v>
       </c>
       <c r="AI8" t="n">
-        <v>185.292556980057</v>
+        <v>185.5155270655271</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06712962962963</v>
+        <v>1.075925925925926</v>
       </c>
       <c r="AK8" t="n">
-        <v>67.18011039886041</v>
+        <v>67.41816239316239</v>
       </c>
       <c r="AL8" t="n">
-        <v>1429728.89957265</v>
+        <v>1430449.786324786</v>
       </c>
       <c r="AM8" t="n">
-        <v>72.81997863247862</v>
+        <v>72.78931623931622</v>
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr">
@@ -1525,22 +1525,22 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>26.95454545454546</v>
+        <v>27.01090909090909</v>
       </c>
       <c r="W9" t="n">
-        <v>184.7045454545455</v>
+        <v>184.9454545454546</v>
       </c>
       <c r="X9" t="n">
-        <v>1.613636363636363</v>
+        <v>1.629090909090909</v>
       </c>
       <c r="Y9" t="n">
-        <v>75.83333333333333</v>
+        <v>75.80727272727273</v>
       </c>
       <c r="Z9" t="n">
-        <v>8471212.121212121</v>
+        <v>8416181.818181818</v>
       </c>
       <c r="AA9" t="n">
-        <v>78.16666666666667</v>
+        <v>78.08000000000001</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1549,22 +1549,22 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>27.32126322751323</v>
+        <v>26.84057934691802</v>
       </c>
       <c r="AI9" t="n">
-        <v>184.4416335978836</v>
+        <v>183.9944046710981</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.525628306878307</v>
+        <v>1.480745523228361</v>
       </c>
       <c r="AK9" t="n">
-        <v>73.8738425925926</v>
+        <v>73.74021230612765</v>
       </c>
       <c r="AL9" t="n">
-        <v>5045312.500000001</v>
+        <v>5214261.759471141</v>
       </c>
       <c r="AM9" t="n">
-        <v>75.86044973544975</v>
+        <v>76.13055464748828</v>
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr">
@@ -1638,22 +1638,22 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>25.45090909090909</v>
+        <v>25.27979797979798</v>
       </c>
       <c r="W10" t="n">
-        <v>183.8375757575758</v>
+        <v>183.9555555555555</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>68.32727272727273</v>
+        <v>68.37878787878789</v>
       </c>
       <c r="Z10" t="n">
-        <v>1664621.212121212</v>
+        <v>1701830.808080808</v>
       </c>
       <c r="AA10" t="n">
-        <v>71.40000000000001</v>
+        <v>71.61111111111111</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1662,22 +1662,22 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>26.25085542688517</v>
+        <v>26.1187684112932</v>
       </c>
       <c r="AI10" t="n">
-        <v>182.0268557042585</v>
+        <v>182.0825649387339</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>67.49964153356602</v>
+        <v>67.475009919947</v>
       </c>
       <c r="AL10" t="n">
-        <v>1425058.387074406</v>
+        <v>1445442.174413857</v>
       </c>
       <c r="AM10" t="n">
-        <v>70.55308770388862</v>
+        <v>70.65766567916643</v>
       </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr">
@@ -1755,22 +1755,22 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>24.86136363636364</v>
+        <v>25.01515151515152</v>
       </c>
       <c r="W11" t="n">
-        <v>182.7712121212121</v>
+        <v>182.7034090909091</v>
       </c>
       <c r="X11" t="n">
-        <v>2.081818181818182</v>
+        <v>2.114772727272727</v>
       </c>
       <c r="Y11" t="n">
-        <v>80.17954545454546</v>
+        <v>80.2594696969697</v>
       </c>
       <c r="Z11" t="n">
-        <v>28639015.15151516</v>
+        <v>28676704.54545455</v>
       </c>
       <c r="AA11" t="n">
-        <v>83.68712121212121</v>
+        <v>83.63409090909092</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1779,22 +1779,22 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>25.23296957671957</v>
+        <v>24.78276685070163</v>
       </c>
       <c r="AI11" t="n">
-        <v>185.6076029445595</v>
+        <v>185.307395905222</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.636703473659996</v>
+        <v>1.666533672647803</v>
       </c>
       <c r="AK11" t="n">
-        <v>76.14737893949849</v>
+        <v>76.70394453071084</v>
       </c>
       <c r="AL11" t="n">
-        <v>15484254.94593973</v>
+        <v>17697117.9836669</v>
       </c>
       <c r="AM11" t="n">
-        <v>80.69870744191398</v>
+        <v>81.43627070393374</v>
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr">
@@ -1859,76 +1859,76 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>25.58671328671329</v>
+        <v>25.55090909090909</v>
       </c>
       <c r="Q12" t="n">
-        <v>183.6125874125874</v>
+        <v>183.4945454545455</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>67.12027972027974</v>
+        <v>67.17090909090909</v>
       </c>
       <c r="T12" t="n">
-        <v>1415332.167832168</v>
+        <v>1433590.909090909</v>
       </c>
       <c r="U12" t="n">
-        <v>71.00909090909092</v>
+        <v>71.06242424242424</v>
       </c>
       <c r="V12" t="n">
-        <v>27.25174825174825</v>
+        <v>27.23484848484849</v>
       </c>
       <c r="W12" t="n">
-        <v>183.6153846153846</v>
+        <v>183.7840909090909</v>
       </c>
       <c r="X12" t="n">
-        <v>1.713286713286713</v>
+        <v>1.712121212121212</v>
       </c>
       <c r="Y12" t="n">
-        <v>75.54545454545453</v>
+        <v>75.54924242424242</v>
       </c>
       <c r="Z12" t="n">
-        <v>9070629.370629372</v>
+        <v>9118181.818181818</v>
       </c>
       <c r="AA12" t="n">
-        <v>77.37062937062936</v>
+        <v>77.40151515151516</v>
       </c>
       <c r="AB12" t="n">
-        <v>26.1256105006105</v>
+        <v>26.20886243386243</v>
       </c>
       <c r="AC12" t="n">
-        <v>184.8692002442002</v>
+        <v>185.1949735449735</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>66.59783272283272</v>
+        <v>66.5681216931217</v>
       </c>
       <c r="AF12" t="n">
-        <v>1186095.848595849</v>
+        <v>1171283.068783069</v>
       </c>
       <c r="AG12" t="n">
-        <v>69.75152625152624</v>
+        <v>69.75132275132275</v>
       </c>
       <c r="AH12" t="n">
-        <v>24.84033802454855</v>
+        <v>24.99484444807672</v>
       </c>
       <c r="AI12" t="n">
-        <v>185.1910384936701</v>
+        <v>184.9159408560653</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.448115481010218</v>
+        <v>1.470589479435303</v>
       </c>
       <c r="AK12" t="n">
-        <v>73.21261487050961</v>
+        <v>73.55038975003936</v>
       </c>
       <c r="AL12" t="n">
-        <v>5536173.767752716</v>
+        <v>6272273.95367949</v>
       </c>
       <c r="AM12" t="n">
-        <v>76.55806182121972</v>
+        <v>76.75503260339859</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -1999,22 +1999,22 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>25.92424242424243</v>
+        <v>25.89015151515151</v>
       </c>
       <c r="W13" t="n">
-        <v>186.5151515151515</v>
+        <v>186.7159090909091</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>72.82575757575758</v>
+        <v>72.85606060606061</v>
       </c>
       <c r="Z13" t="n">
-        <v>4325000</v>
+        <v>4351988.636363637</v>
       </c>
       <c r="AA13" t="n">
-        <v>75.07575757575758</v>
+        <v>75.10606060606061</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -2023,22 +2023,22 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>27.23875661375661</v>
+        <v>27.16863641591902</v>
       </c>
       <c r="AI13" t="n">
-        <v>183.2333002645503</v>
+        <v>182.88109615827</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>68.90112433862434</v>
+        <v>69.30280581435473</v>
       </c>
       <c r="AL13" t="n">
-        <v>1635300.925925926</v>
+        <v>1835307.126322751</v>
       </c>
       <c r="AM13" t="n">
-        <v>70.67410714285715</v>
+        <v>71.03622469519208</v>
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr">
@@ -2116,22 +2116,22 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>25.12878787878788</v>
+        <v>25.13939393939394</v>
       </c>
       <c r="W14" t="n">
-        <v>186.1590909090909</v>
+        <v>186.0848484848485</v>
       </c>
       <c r="X14" t="n">
-        <v>1.083333333333333</v>
+        <v>1.078787878787879</v>
       </c>
       <c r="Y14" t="n">
-        <v>68.63636363636364</v>
+        <v>68.64242424242424</v>
       </c>
       <c r="Z14" t="n">
-        <v>1782954.545454546</v>
+        <v>1786969.696969697</v>
       </c>
       <c r="AA14" t="n">
-        <v>72.62121212121212</v>
+        <v>72.60606060606059</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -2140,22 +2140,22 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>24.96303485162181</v>
+        <v>24.97135380722337</v>
       </c>
       <c r="AI14" t="n">
-        <v>186.1707930756844</v>
+        <v>186.3218196457327</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.007591442374051</v>
+        <v>1.006073153899241</v>
       </c>
       <c r="AK14" t="n">
-        <v>66.23001495284103</v>
+        <v>66.1043823326432</v>
       </c>
       <c r="AL14" t="n">
-        <v>1316034.226190476</v>
+        <v>1264679.232804233</v>
       </c>
       <c r="AM14" t="n">
-        <v>71.01655595813205</v>
+        <v>70.90954106280194</v>
       </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr">
@@ -2233,22 +2233,22 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>25.88636363636364</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="W15" t="n">
-        <v>183.7045454545454</v>
+        <v>183.6121212121212</v>
       </c>
       <c r="X15" t="n">
-        <v>1.181818181818182</v>
+        <v>1.16969696969697</v>
       </c>
       <c r="Y15" t="n">
-        <v>69.7878787878788</v>
+        <v>69.7818181818182</v>
       </c>
       <c r="Z15" t="n">
-        <v>2027462.121212121</v>
+        <v>2006363.636363636</v>
       </c>
       <c r="AA15" t="n">
-        <v>73.78787878787878</v>
+        <v>73.73333333333333</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2257,22 +2257,22 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>24.09920634920634</v>
+        <v>24.07195767195767</v>
       </c>
       <c r="AI15" t="n">
-        <v>184.1808862433863</v>
+        <v>184.3002645502646</v>
       </c>
       <c r="AJ15" t="n">
         <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>66.04050925925925</v>
+        <v>66.04722222222222</v>
       </c>
       <c r="AL15" t="n">
-        <v>1296275.628306878</v>
+        <v>1300539.021164021</v>
       </c>
       <c r="AM15" t="n">
-        <v>71.49007936507935</v>
+        <v>71.710582010582</v>
       </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr">
@@ -2350,22 +2350,22 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>25.84090909090909</v>
+        <v>25.80681818181818</v>
       </c>
       <c r="W16" t="n">
-        <v>184.4318181818182</v>
+        <v>184.4621212121212</v>
       </c>
       <c r="X16" t="n">
-        <v>2.310606060606061</v>
+        <v>2.321969696969697</v>
       </c>
       <c r="Y16" t="n">
-        <v>80.18939393939394</v>
+        <v>80.24621212121212</v>
       </c>
       <c r="Z16" t="n">
-        <v>29079545.45454545</v>
+        <v>29456060.60606061</v>
       </c>
       <c r="AA16" t="n">
-        <v>83.04545454545455</v>
+        <v>83.11742424242425</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2374,22 +2374,22 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>24.72106481481481</v>
+        <v>24.83647486772487</v>
       </c>
       <c r="AI16" t="n">
-        <v>184.0613425925926</v>
+        <v>183.855076058201</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.925925925925926</v>
+        <v>1.949900793650794</v>
       </c>
       <c r="AK16" t="n">
-        <v>76.91319444444444</v>
+        <v>77.17939814814815</v>
       </c>
       <c r="AL16" t="n">
-        <v>17697453.70370371</v>
+        <v>18144204.6957672</v>
       </c>
       <c r="AM16" t="n">
-        <v>82.01041666666667</v>
+        <v>82.01909722222221</v>
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr">
@@ -2467,22 +2467,22 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>23.57342657342657</v>
+        <v>23.75151515151515</v>
       </c>
       <c r="W17" t="n">
-        <v>183.8321678321678</v>
+        <v>183.9030303030303</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>67.34965034965035</v>
+        <v>67.47272727272727</v>
       </c>
       <c r="Z17" t="n">
-        <v>1655594.405594406</v>
+        <v>1659090.909090909</v>
       </c>
       <c r="AA17" t="n">
-        <v>73.20979020979021</v>
+        <v>73.03636363636363</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2491,22 +2491,22 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>26.61635586635587</v>
+        <v>26.40824915824916</v>
       </c>
       <c r="AI17" t="n">
-        <v>182.894425019425</v>
+        <v>183.167760942761</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>66.96950271950271</v>
+        <v>66.72912457912459</v>
       </c>
       <c r="AL17" t="n">
-        <v>1126702.117327117</v>
+        <v>1104993.686868687</v>
       </c>
       <c r="AM17" t="n">
-        <v>69.7441724941725</v>
+        <v>69.79309764309764</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -2577,22 +2577,22 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>25.61111111111111</v>
+        <v>25.65046296296296</v>
       </c>
       <c r="W18" t="n">
-        <v>185.8571548821549</v>
+        <v>185.8619107744108</v>
       </c>
       <c r="X18" t="n">
-        <v>1.467676767676767</v>
+        <v>1.45976430976431</v>
       </c>
       <c r="Y18" t="n">
-        <v>74.52407407407406</v>
+        <v>74.625</v>
       </c>
       <c r="Z18" t="n">
-        <v>6665492.424242425</v>
+        <v>6710662.878787879</v>
       </c>
       <c r="AA18" t="n">
-        <v>77.1476430976431</v>
+        <v>77.19234006734007</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2601,22 +2601,22 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>24.26052979671401</v>
+        <v>24.30819129718607</v>
       </c>
       <c r="AI18" t="n">
-        <v>184.0027760373156</v>
+        <v>183.6187468960205</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.157494430520746</v>
+        <v>1.147585874129024</v>
       </c>
       <c r="AK18" t="n">
-        <v>71.26524644945698</v>
+        <v>71.62761588453829</v>
       </c>
       <c r="AL18" t="n">
-        <v>3826866.428223337</v>
+        <v>4006952.868060768</v>
       </c>
       <c r="AM18" t="n">
-        <v>76.35502819548871</v>
+        <v>76.3987690673691</v>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
@@ -2683,22 +2683,22 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>24.09696969696969</v>
+        <v>24.03515151515152</v>
       </c>
       <c r="W19" t="n">
-        <v>185.5136363636364</v>
+        <v>185.7927272727273</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>66.76060606060607</v>
+        <v>66.72363636363637</v>
       </c>
       <c r="Z19" t="n">
-        <v>1471231.060606061</v>
+        <v>1459409.090909091</v>
       </c>
       <c r="AA19" t="n">
-        <v>72.39999999999999</v>
+        <v>72.31393939393939</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2707,22 +2707,22 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>24.86836533032185</v>
+        <v>24.71506263462785</v>
       </c>
       <c r="AI19" t="n">
-        <v>186.1097896668549</v>
+        <v>185.7294984001506</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>66.78628482025221</v>
+        <v>66.6373611895351</v>
       </c>
       <c r="AL19" t="n">
-        <v>1347329.074910597</v>
+        <v>1347724.371039589</v>
       </c>
       <c r="AM19" t="n">
-        <v>71.6701075192923</v>
+        <v>71.76849342284125</v>
       </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr">
@@ -2794,76 +2794,76 @@
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>26.53560606060606</v>
+        <v>26.54969696969697</v>
       </c>
       <c r="Q20" t="n">
-        <v>184.0522727272727</v>
+        <v>184.3387878787879</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>67.80909090909091</v>
+        <v>67.76242424242425</v>
       </c>
       <c r="T20" t="n">
-        <v>1331609.848484848</v>
+        <v>1327106.060606061</v>
       </c>
       <c r="U20" t="n">
-        <v>70.56060606060606</v>
+        <v>70.56363636363636</v>
       </c>
       <c r="V20" t="n">
-        <v>23.95227272727273</v>
+        <v>24.26306818181818</v>
       </c>
       <c r="W20" t="n">
-        <v>184.6340909090909</v>
+        <v>184.7460227272728</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.073863636363636</v>
       </c>
       <c r="Y20" t="n">
-        <v>70.46742424242424</v>
+        <v>70.53920454545454</v>
       </c>
       <c r="Z20" t="n">
-        <v>2845984.848484848</v>
+        <v>2805454.545454545</v>
       </c>
       <c r="AA20" t="n">
-        <v>75.64242424242424</v>
+        <v>75.48295454545455</v>
       </c>
       <c r="AB20" t="n">
-        <v>24.94931130664827</v>
+        <v>24.73087761674718</v>
       </c>
       <c r="AC20" t="n">
-        <v>183.5745485392224</v>
+        <v>183.3894007361399</v>
       </c>
       <c r="AD20" t="n">
         <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>66.53948844030366</v>
+        <v>66.39468599033816</v>
       </c>
       <c r="AF20" t="n">
-        <v>1217487.275707384</v>
+        <v>1208483.868184955</v>
       </c>
       <c r="AG20" t="n">
-        <v>70.42798194156889</v>
+        <v>70.55429031515989</v>
       </c>
       <c r="AH20" t="n">
-        <v>26.23930372428656</v>
+        <v>25.91930914242127</v>
       </c>
       <c r="AI20" t="n">
-        <v>183.6655943905658</v>
+        <v>183.1085707929244</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.239149352850726</v>
+        <v>1.209991974955505</v>
       </c>
       <c r="AK20" t="n">
-        <v>68.87934510188516</v>
+        <v>68.57220723911227</v>
       </c>
       <c r="AL20" t="n">
-        <v>1680755.670880099</v>
+        <v>1682609.16387436</v>
       </c>
       <c r="AM20" t="n">
-        <v>73.24138849539308</v>
+        <v>73.19443422868767</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -2934,22 +2934,22 @@
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>25.13286713286713</v>
+        <v>25.08484848484848</v>
       </c>
       <c r="W21" t="n">
-        <v>182.4755244755245</v>
+        <v>182.4909090909091</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>67.19580419580419</v>
+        <v>67.2909090909091</v>
       </c>
       <c r="Z21" t="n">
-        <v>1318951.048951049</v>
+        <v>1338393.93939394</v>
       </c>
       <c r="AA21" t="n">
-        <v>70.92307692307692</v>
+        <v>70.96969696969697</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2958,22 +2958,22 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="n">
-        <v>28.06135531135531</v>
+        <v>27.9031746031746</v>
       </c>
       <c r="AI21" t="n">
-        <v>181.1076698155645</v>
+        <v>181.1016471734893</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>64.0467868388921</v>
+        <v>64.24054859370649</v>
       </c>
       <c r="AL21" t="n">
-        <v>712781.6978343294</v>
+        <v>731285.8047897521</v>
       </c>
       <c r="AM21" t="n">
-        <v>65.57185913501704</v>
+        <v>65.70394458368143</v>
       </c>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr">
@@ -3051,22 +3051,22 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>27.96444444444445</v>
+        <v>27.92777777777778</v>
       </c>
       <c r="W22" t="n">
-        <v>183.0874074074074</v>
+        <v>183.1965811965812</v>
       </c>
       <c r="X22" t="n">
-        <v>1.262962962962963</v>
+        <v>1.265811965811966</v>
       </c>
       <c r="Y22" t="n">
-        <v>73.14888888888888</v>
+        <v>73.1794871794872</v>
       </c>
       <c r="Z22" t="n">
-        <v>3618777.777777778</v>
+        <v>3630032.051282051</v>
       </c>
       <c r="AA22" t="n">
-        <v>75.07185185185185</v>
+        <v>75.15897435897435</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
@@ -3075,22 +3075,22 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>26.99601503759398</v>
+        <v>26.73745421245421</v>
       </c>
       <c r="AI22" t="n">
-        <v>183.0080785296574</v>
+        <v>182.4158289460349</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.042106655527708</v>
+        <v>1.04545714900406</v>
       </c>
       <c r="AK22" t="n">
-        <v>69.90181147312727</v>
+        <v>70.09494745973578</v>
       </c>
       <c r="AL22" t="n">
-        <v>2059198.203842941</v>
+        <v>2184121.574697233</v>
       </c>
       <c r="AM22" t="n">
-        <v>72.83213032581452</v>
+        <v>73.0017850665734</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -3172,22 +3172,22 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>24.41666666666667</v>
+        <v>24.37878787878788</v>
       </c>
       <c r="W23" t="n">
-        <v>185.1818181818182</v>
+        <v>185.1439393939394</v>
       </c>
       <c r="X23" t="n">
         <v>1.295454545454546</v>
       </c>
       <c r="Y23" t="n">
-        <v>72.54545454545455</v>
+        <v>72.5719696969697</v>
       </c>
       <c r="Z23" t="n">
-        <v>5916666.666666667</v>
+        <v>5912878.787878788</v>
       </c>
       <c r="AA23" t="n">
-        <v>77.82575757575758</v>
+        <v>77.85606060606061</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
@@ -3196,22 +3196,22 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>26.0925925925926</v>
+        <v>25.79629629629629</v>
       </c>
       <c r="AI23" t="n">
-        <v>185.7731481481481</v>
+        <v>185.338210978836</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.28587962962963</v>
+        <v>1.261739417989418</v>
       </c>
       <c r="AK23" t="n">
-        <v>69.21875</v>
+        <v>69.37003968253968</v>
       </c>
       <c r="AL23" t="n">
-        <v>2556354.166666667</v>
+        <v>2715412.533068783</v>
       </c>
       <c r="AM23" t="n">
-        <v>74.13194444444444</v>
+        <v>74.37838955026456</v>
       </c>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr">
@@ -3282,22 +3282,22 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>26.13013468013468</v>
+        <v>26.21919191919192</v>
       </c>
       <c r="W24" t="n">
-        <v>185.9308080808081</v>
+        <v>185.9505892255892</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>70.72407407407407</v>
+        <v>70.73985690235691</v>
       </c>
       <c r="Z24" t="n">
-        <v>2406159.511784512</v>
+        <v>2382124.368686868</v>
       </c>
       <c r="AA24" t="n">
-        <v>73.77020202020202</v>
+        <v>73.69482323232323</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
@@ -3306,22 +3306,22 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>26.33363526570048</v>
+        <v>26.09022927407678</v>
       </c>
       <c r="AI24" t="n">
-        <v>187.8852297561537</v>
+        <v>187.1591262652404</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>68.41533672647803</v>
+        <v>68.58049072890024</v>
       </c>
       <c r="AL24" t="n">
-        <v>1512004.50741891</v>
+        <v>1616511.003404985</v>
       </c>
       <c r="AM24" t="n">
-        <v>71.24547101449276</v>
+        <v>71.57790316005629</v>
       </c>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr">
@@ -3392,22 +3392,22 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>26.76515151515152</v>
+        <v>27.00606060606061</v>
       </c>
       <c r="W25" t="n">
-        <v>183.6969696969697</v>
+        <v>183.7333333333333</v>
       </c>
       <c r="X25" t="n">
-        <v>1.015151515151515</v>
+        <v>1.012121212121212</v>
       </c>
       <c r="Y25" t="n">
-        <v>68.82575757575758</v>
+        <v>68.92121212121212</v>
       </c>
       <c r="Z25" t="n">
-        <v>1653598.484848485</v>
+        <v>1640000</v>
       </c>
       <c r="AA25" t="n">
-        <v>72.91666666666666</v>
+        <v>72.76363636363635</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -3416,22 +3416,22 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="n">
-        <v>26.71164021164021</v>
+        <v>26.53968253968254</v>
       </c>
       <c r="AI25" t="n">
-        <v>182.818287037037</v>
+        <v>183.0027777777777</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.148809523809524</v>
+        <v>1.119047619047619</v>
       </c>
       <c r="AK25" t="n">
-        <v>66.69345238095238</v>
+        <v>66.70291005291006</v>
       </c>
       <c r="AL25" t="n">
-        <v>1143047.288359788</v>
+        <v>1142956.349206349</v>
       </c>
       <c r="AM25" t="n">
-        <v>71.34705687830687</v>
+        <v>71.3739417989418</v>
       </c>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr">
@@ -3509,22 +3509,22 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>24.60909090909091</v>
+        <v>24.6569696969697</v>
       </c>
       <c r="W26" t="n">
-        <v>183.4901515151516</v>
+        <v>183.4224242424243</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>70.76666666666667</v>
+        <v>70.77696969696969</v>
       </c>
       <c r="Z26" t="n">
-        <v>2784090.909090909</v>
+        <v>2776363.636363636</v>
       </c>
       <c r="AA26" t="n">
-        <v>74.59469696969698</v>
+        <v>74.53636363636363</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
@@ -3533,22 +3533,22 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="n">
-        <v>25.29377104377105</v>
+        <v>25.16001683501684</v>
       </c>
       <c r="AI26" t="n">
-        <v>181.7002765752766</v>
+        <v>181.9852212602213</v>
       </c>
       <c r="AJ26" t="n">
         <v>1</v>
       </c>
       <c r="AK26" t="n">
-        <v>69.56464947089948</v>
+        <v>69.51005291005292</v>
       </c>
       <c r="AL26" t="n">
-        <v>2275444.925444926</v>
+        <v>2252022.607022607</v>
       </c>
       <c r="AM26" t="n">
-        <v>72.93924362674363</v>
+        <v>73.00972823472824</v>
       </c>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr">
@@ -3626,22 +3626,22 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>25.10909090909091</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="W27" t="n">
-        <v>184.369696969697</v>
+        <v>184.4848484848485</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>70.22424242424243</v>
+        <v>70.1919191919192</v>
       </c>
       <c r="Z27" t="n">
-        <v>2589090.909090909</v>
+        <v>2569696.96969697</v>
       </c>
       <c r="AA27" t="n">
-        <v>74.17575757575757</v>
+        <v>74.17676767676767</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
@@ -3650,22 +3650,22 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>23.77962962962963</v>
+        <v>23.50694444444444</v>
       </c>
       <c r="AI27" t="n">
-        <v>186.0240740740741</v>
+        <v>186.0601851851852</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>66.66666666666667</v>
+        <v>66.11882716049382</v>
       </c>
       <c r="AL27" t="n">
-        <v>1633064.814814815</v>
+        <v>1558275.462962963</v>
       </c>
       <c r="AM27" t="n">
-        <v>72.25648148148149</v>
+        <v>72.07793209876543</v>
       </c>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr">
@@ -3741,76 +3741,76 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>25.5560606060606</v>
+        <v>25.53430602319492</v>
       </c>
       <c r="Q28" t="n">
-        <v>184.6888888888889</v>
+        <v>184.4677141788253</v>
       </c>
       <c r="R28" t="n">
-        <v>2.152597402597403</v>
+        <v>2.169322858211747</v>
       </c>
       <c r="S28" t="n">
-        <v>81.704329004329</v>
+        <v>81.66719042274597</v>
       </c>
       <c r="T28" t="n">
-        <v>36913708.51370852</v>
+        <v>37101945.37972316</v>
       </c>
       <c r="U28" t="n">
-        <v>84.44848484848485</v>
+        <v>84.42667414889638</v>
       </c>
       <c r="V28" t="n">
-        <v>24.35606060606061</v>
+        <v>24.39272727272727</v>
       </c>
       <c r="W28" t="n">
         <v>184.7272727272727</v>
       </c>
       <c r="X28" t="n">
-        <v>1.545454545454545</v>
+        <v>1.534545454545454</v>
       </c>
       <c r="Y28" t="n">
-        <v>76.1969696969697</v>
+        <v>76.11272727272728</v>
       </c>
       <c r="Z28" t="n">
-        <v>11916666.66666666</v>
+        <v>11664000</v>
       </c>
       <c r="AA28" t="n">
-        <v>79.14393939393939</v>
+        <v>79.00000000000001</v>
       </c>
       <c r="AB28" t="n">
-        <v>23.06161369686215</v>
+        <v>23.14342195458392</v>
       </c>
       <c r="AC28" t="n">
-        <v>182.2996733080584</v>
+        <v>182.3085980685746</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.584457933370977</v>
+        <v>1.597039333805161</v>
       </c>
       <c r="AE28" t="n">
-        <v>77.4817092845043</v>
+        <v>77.56414795711771</v>
       </c>
       <c r="AF28" t="n">
-        <v>27706889.09111075</v>
+        <v>27738496.98608804</v>
       </c>
       <c r="AG28" t="n">
-        <v>83.52708014035655</v>
+        <v>83.48672153563776</v>
       </c>
       <c r="AH28" t="n">
-        <v>24.19146825396825</v>
+        <v>23.86049137336094</v>
       </c>
       <c r="AI28" t="n">
-        <v>183.0720899470899</v>
+        <v>182.7170835058661</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.242559523809524</v>
+        <v>1.253840579710145</v>
       </c>
       <c r="AK28" t="n">
-        <v>70.49652777777777</v>
+        <v>71.08787370600413</v>
       </c>
       <c r="AL28" t="n">
-        <v>4968282.903439154</v>
+        <v>5865789.216701174</v>
       </c>
       <c r="AM28" t="n">
-        <v>75.63210978835978</v>
+        <v>76.36166666666666</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>

--- a/p6_deployment/data/germany/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO28"/>
+  <dimension ref="A1:AO32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>25.93048128342246</v>
+        <v>25.97727272727273</v>
       </c>
       <c r="Q3" t="n">
-        <v>185.5828877005348</v>
+        <v>185.6306818181818</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>67.12299465240642</v>
+        <v>67.11363636363636</v>
       </c>
       <c r="T3" t="n">
-        <v>1207620.320855615</v>
+        <v>1198721.590909091</v>
       </c>
       <c r="U3" t="n">
-        <v>69.77540106951871</v>
+        <v>69.70454545454545</v>
       </c>
       <c r="V3" t="n">
         <v>25.88363636363636</v>
@@ -854,22 +854,22 @@
         <v>78.27272727272728</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.63643790849673</v>
+        <v>24.62760416666667</v>
       </c>
       <c r="AC3" t="n">
-        <v>184.0024509803922</v>
+        <v>184.0234375</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>64.77205882352941</v>
+        <v>64.81336805555554</v>
       </c>
       <c r="AF3" t="n">
-        <v>957536.7647058824</v>
+        <v>966861.9791666667</v>
       </c>
       <c r="AG3" t="n">
-        <v>68.62254901960785</v>
+        <v>68.68923611111111</v>
       </c>
       <c r="AH3" t="n">
         <v>26.10392546583851</v>
@@ -1042,8 +1042,15 @@
   ger </t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>19500</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>tbC3EcQn</t>
@@ -1099,7 +1106,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>24.87941074758151</v>
+        <v>24.87941074758152</v>
       </c>
       <c r="AI5" t="n">
         <v>182.0659746643728</v>
@@ -1108,7 +1115,7 @@
         <v>2.147727117943079</v>
       </c>
       <c r="AK5" t="n">
-        <v>77.91587622678512</v>
+        <v>77.91587622678513</v>
       </c>
       <c r="AL5" t="n">
         <v>26298143.27481081</v>
@@ -1492,8 +1499,15 @@
   ger </t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4990</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Q1yNyI5t</t>
@@ -1638,22 +1652,22 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>25.27979797979798</v>
+        <v>25.32299465240642</v>
       </c>
       <c r="W10" t="n">
-        <v>183.9555555555555</v>
+        <v>183.8994652406417</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>68.37878787878789</v>
+        <v>68.35828877005349</v>
       </c>
       <c r="Z10" t="n">
-        <v>1701830.808080808</v>
+        <v>1690708.556149733</v>
       </c>
       <c r="AA10" t="n">
-        <v>71.61111111111111</v>
+        <v>71.55080213903743</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1662,22 +1676,22 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>26.1187684112932</v>
+        <v>26.18457831783986</v>
       </c>
       <c r="AI10" t="n">
-        <v>182.0825649387339</v>
+        <v>182.0612779089863</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>67.475009919947</v>
+        <v>67.48334383680663</v>
       </c>
       <c r="AL10" t="n">
-        <v>1445442.174413857</v>
+        <v>1437494.328464345</v>
       </c>
       <c r="AM10" t="n">
-        <v>70.65766567916643</v>
+        <v>70.6244564707514</v>
       </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr">
@@ -1779,7 +1793,7 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>24.78276685070163</v>
+        <v>24.78276685070164</v>
       </c>
       <c r="AI11" t="n">
         <v>185.307395905222</v>
@@ -1828,8 +1842,15 @@
   ger </t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>16667</v>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>88Xgj1Y5</t>
@@ -1966,8 +1987,15 @@
   ger </t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>8000</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>lKLJUxeT</t>
@@ -1999,22 +2027,22 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>25.89015151515151</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="W13" t="n">
-        <v>186.7159090909091</v>
+        <v>186.6600790513834</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>72.85606060606061</v>
+        <v>72.84584980237155</v>
       </c>
       <c r="Z13" t="n">
-        <v>4351988.636363637</v>
+        <v>4341600.790513834</v>
       </c>
       <c r="AA13" t="n">
-        <v>75.10606060606061</v>
+        <v>75.09090909090909</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -2023,22 +2051,22 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>27.16863641591902</v>
+        <v>27.13732109100729</v>
       </c>
       <c r="AI13" t="n">
-        <v>182.88109615827</v>
+        <v>182.9290665226393</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>69.30280581435473</v>
+        <v>69.29181669517209</v>
       </c>
       <c r="AL13" t="n">
-        <v>1835307.126322751</v>
+        <v>1847953.329882677</v>
       </c>
       <c r="AM13" t="n">
-        <v>71.03622469519208</v>
+        <v>71.04263059981396</v>
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr">
@@ -2116,22 +2144,22 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>25.13939393939394</v>
+        <v>25.11688311688312</v>
       </c>
       <c r="W14" t="n">
-        <v>186.0848484848485</v>
+        <v>186.1233766233766</v>
       </c>
       <c r="X14" t="n">
-        <v>1.078787878787879</v>
+        <v>1.077922077922078</v>
       </c>
       <c r="Y14" t="n">
-        <v>68.64242424242424</v>
+        <v>68.64935064935064</v>
       </c>
       <c r="Z14" t="n">
-        <v>1786969.696969697</v>
+        <v>1789935.064935065</v>
       </c>
       <c r="AA14" t="n">
-        <v>72.60606060606059</v>
+        <v>72.63636363636364</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -2140,22 +2168,22 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>24.97135380722337</v>
+        <v>24.93359336488218</v>
       </c>
       <c r="AI14" t="n">
-        <v>186.3218196457327</v>
+        <v>186.3180210489993</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.006073153899241</v>
+        <v>1.006506950606329</v>
       </c>
       <c r="AK14" t="n">
-        <v>66.1043823326432</v>
+        <v>66.12969535640343</v>
       </c>
       <c r="AL14" t="n">
-        <v>1264679.232804233</v>
+        <v>1283584.892290249</v>
       </c>
       <c r="AM14" t="n">
-        <v>70.90954106280194</v>
+        <v>70.97450828157351</v>
       </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr">
@@ -2350,22 +2378,22 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>25.80681818181818</v>
+        <v>25.8300395256917</v>
       </c>
       <c r="W16" t="n">
-        <v>184.4621212121212</v>
+        <v>184.4901185770751</v>
       </c>
       <c r="X16" t="n">
-        <v>2.321969696969697</v>
+        <v>2.33201581027668</v>
       </c>
       <c r="Y16" t="n">
-        <v>80.24621212121212</v>
+        <v>80.31225296442688</v>
       </c>
       <c r="Z16" t="n">
-        <v>29456060.60606061</v>
+        <v>29751383.39920948</v>
       </c>
       <c r="AA16" t="n">
-        <v>83.11742424242425</v>
+        <v>83.15415019762845</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2374,22 +2402,22 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>24.83647486772487</v>
+        <v>24.84385783298827</v>
       </c>
       <c r="AI16" t="n">
-        <v>183.855076058201</v>
+        <v>183.8487750172533</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.949900793650794</v>
+        <v>1.962215320910973</v>
       </c>
       <c r="AK16" t="n">
-        <v>77.17939814814815</v>
+        <v>77.3852657004831</v>
       </c>
       <c r="AL16" t="n">
-        <v>18144204.6957672</v>
+        <v>18611827.12215321</v>
       </c>
       <c r="AM16" t="n">
-        <v>82.01909722222221</v>
+        <v>82.16485507246377</v>
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr">
@@ -2616,7 +2644,7 @@
         <v>4006952.868060768</v>
       </c>
       <c r="AM18" t="n">
-        <v>76.3987690673691</v>
+        <v>76.39876906736912</v>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
@@ -2812,22 +2840,22 @@
         <v>70.56363636363636</v>
       </c>
       <c r="V20" t="n">
-        <v>24.26306818181818</v>
+        <v>24.13515151515151</v>
       </c>
       <c r="W20" t="n">
-        <v>184.7460227272728</v>
+        <v>184.7472727272728</v>
       </c>
       <c r="X20" t="n">
-        <v>1.073863636363636</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="Y20" t="n">
-        <v>70.53920454545454</v>
+        <v>70.52060606060606</v>
       </c>
       <c r="Z20" t="n">
-        <v>2805454.545454545</v>
+        <v>2836121.212121212</v>
       </c>
       <c r="AA20" t="n">
-        <v>75.48295454545455</v>
+        <v>75.59393939393939</v>
       </c>
       <c r="AB20" t="n">
         <v>24.73087761674718</v>
@@ -2848,22 +2876,22 @@
         <v>70.55429031515989</v>
       </c>
       <c r="AH20" t="n">
-        <v>25.91930914242127</v>
+        <v>25.90440594239221</v>
       </c>
       <c r="AI20" t="n">
-        <v>183.1085707929244</v>
+        <v>183.115808845786</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.209991974955505</v>
+        <v>1.214467630428729</v>
       </c>
       <c r="AK20" t="n">
-        <v>68.57220723911227</v>
+        <v>68.62940200743405</v>
       </c>
       <c r="AL20" t="n">
-        <v>1682609.16387436</v>
+        <v>1668354.536704079</v>
       </c>
       <c r="AM20" t="n">
-        <v>73.19443422868767</v>
+        <v>73.29311079631447</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -2901,8 +2929,15 @@
   ger </t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>10000</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>E3xs5mIe</t>
@@ -3211,7 +3246,7 @@
         <v>2715412.533068783</v>
       </c>
       <c r="AM23" t="n">
-        <v>74.37838955026456</v>
+        <v>74.37838955026454</v>
       </c>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr">
@@ -3315,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>68.58049072890024</v>
+        <v>68.58049072890026</v>
       </c>
       <c r="AL24" t="n">
         <v>1616511.003404985</v>
@@ -3355,8 +3390,15 @@
   ger </t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>10059</v>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>hjNlCFPB</t>
@@ -3392,22 +3434,22 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>27.00606060606061</v>
+        <v>26.92857142857143</v>
       </c>
       <c r="W25" t="n">
-        <v>183.7333333333333</v>
+        <v>183.7207792207792</v>
       </c>
       <c r="X25" t="n">
-        <v>1.012121212121212</v>
+        <v>1.012987012987013</v>
       </c>
       <c r="Y25" t="n">
-        <v>68.92121212121212</v>
+        <v>68.8896103896104</v>
       </c>
       <c r="Z25" t="n">
-        <v>1640000</v>
+        <v>1643506.493506493</v>
       </c>
       <c r="AA25" t="n">
-        <v>72.76363636363635</v>
+        <v>72.82467532467531</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -3416,22 +3458,22 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="n">
-        <v>26.53968253968254</v>
+        <v>26.57823129251701</v>
       </c>
       <c r="AI25" t="n">
-        <v>183.0027777777777</v>
+        <v>182.9632936507936</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.119047619047619</v>
+        <v>1.127551020408163</v>
       </c>
       <c r="AK25" t="n">
-        <v>66.70291005291006</v>
+        <v>66.68168934240363</v>
       </c>
       <c r="AL25" t="n">
-        <v>1142956.349206349</v>
+        <v>1140865.929705215</v>
       </c>
       <c r="AM25" t="n">
-        <v>71.3739417989418</v>
+        <v>71.36096938775509</v>
       </c>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr">
@@ -3677,147 +3719,643 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>22450</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6g44VD52</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>59</v>
+      </c>
+      <c r="K28" t="n">
+        <v>593</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>26.06363636363636</v>
+      </c>
+      <c r="W28" t="n">
+        <v>183.7435606060606</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.147348484848485</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>73.18333333333334</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4895804.924242425</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>76.06325757575758</v>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="n">
+        <v>25.19132267943409</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>184.7709140188939</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.259079632202487</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>69.18188095540785</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2794284.061792464</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>74.31118405918177</v>
+      </c>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>xzRzG0VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>20500</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>YJURlaIO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>59</v>
+      </c>
+      <c r="K29" t="n">
+        <v>593</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>25.62857142857143</v>
+      </c>
+      <c r="W29" t="n">
+        <v>181.3642857142857</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1409642.857142857</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>70.42857142857143</v>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="n">
+        <v>23.17202380952381</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>181.225</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>65.63670634920635</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1277291.666666667</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>70.6875</v>
+      </c>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>9500</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>p8wBsqZt</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>59</v>
+      </c>
+      <c r="K30" t="n">
+        <v>593</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>25.55189393939394</v>
+      </c>
+      <c r="W30" t="n">
+        <v>186.2450757575758</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.571212121212121</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>75.99659090909091</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>11083863.63636363</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>79.62916666666666</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="n">
+        <v>24.28577898550725</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>184.1685185185185</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.25829307568438</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>73.47984601449275</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>8048716.787439614</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>78.17277576489532</v>
+      </c>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>23325</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>59</v>
+      </c>
+      <c r="K31" t="n">
+        <v>593</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>25.69090909090909</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>184.7757575757575</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.078787878787879</v>
+      </c>
+      <c r="S31" t="n">
+        <v>67.53333333333333</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1416060.606060606</v>
+      </c>
+      <c r="U31" t="n">
+        <v>71.06666666666666</v>
+      </c>
+      <c r="V31" t="n">
+        <v>24.2054292929293</v>
+      </c>
+      <c r="W31" t="n">
+        <v>183.2920454545455</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.674200336700337</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>76.81498316498316</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>15183578.49326599</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>81.11140572390572</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>26.2462962962963</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>183.4342592592592</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>66.59722222222223</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1237689.814814815</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>24.90495228527349</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>183.5869284349837</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.499156685534395</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>72.18333902939166</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>6228215.411430388</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>78.08648685085412</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>2BYSk4KO</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D32" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t xml:space="preserve">bayarena
   leverkusen </t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="G32" t="n">
         <v>30210</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J32" t="n">
         <v>59</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K32" t="n">
         <v>594</v>
       </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
         <v>2024</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="P28" t="n">
+      <c r="P32" t="n">
         <v>25.53430602319492</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q32" t="n">
         <v>184.4677141788253</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R32" t="n">
         <v>2.169322858211747</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S32" t="n">
         <v>81.66719042274597</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T32" t="n">
         <v>37101945.37972316</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U32" t="n">
         <v>84.42667414889638</v>
       </c>
-      <c r="V28" t="n">
+      <c r="V32" t="n">
         <v>24.39272727272727</v>
       </c>
-      <c r="W28" t="n">
+      <c r="W32" t="n">
         <v>184.7272727272727</v>
       </c>
-      <c r="X28" t="n">
+      <c r="X32" t="n">
         <v>1.534545454545454</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Y32" t="n">
         <v>76.11272727272728</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="Z32" t="n">
         <v>11664000</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AA32" t="n">
         <v>79.00000000000001</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AB32" t="n">
         <v>23.14342195458392</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AC32" t="n">
         <v>182.3085980685746</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AD32" t="n">
         <v>1.597039333805161</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AE32" t="n">
         <v>77.56414795711771</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AF32" t="n">
         <v>27738496.98608804</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AG32" t="n">
         <v>83.48672153563776</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AH32" t="n">
         <v>23.86049137336094</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AI32" t="n">
         <v>182.7170835058661</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AJ32" t="n">
         <v>1.253840579710145</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AK32" t="n">
         <v>71.08787370600413</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AL32" t="n">
         <v>5865789.216701174</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AM32" t="n">
         <v>76.36166666666666</v>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AN32" t="inlineStr">
         <is>
           <t>2BYSk4KO</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="AO32" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>

--- a/p6_deployment/data/germany/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_filled.xlsx
@@ -703,22 +703,22 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>25.84363636363636</v>
+        <v>25.85584415584416</v>
       </c>
       <c r="W2" t="n">
-        <v>184.6181818181818</v>
+        <v>185.0896103896104</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>70.08363636363637</v>
+        <v>69.98311688311688</v>
       </c>
       <c r="Z2" t="n">
-        <v>2310060.606060606</v>
+        <v>2280129.87012987</v>
       </c>
       <c r="AA2" t="n">
-        <v>73.09454545454545</v>
+        <v>72.9948051948052</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -727,22 +727,22 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>26.32033834586466</v>
+        <v>25.9109291084855</v>
       </c>
       <c r="AI2" t="n">
-        <v>186.0177443609022</v>
+        <v>185.9665950590763</v>
       </c>
       <c r="AJ2" t="n">
         <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>66.88057644110276</v>
+        <v>66.73899033297529</v>
       </c>
       <c r="AL2" t="n">
-        <v>1260743.73433584</v>
+        <v>1282843.716433942</v>
       </c>
       <c r="AM2" t="n">
-        <v>70.93689223057645</v>
+        <v>71.16578947368421</v>
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr">
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>25.97727272727273</v>
+        <v>26.1010101010101</v>
       </c>
       <c r="Q3" t="n">
-        <v>185.6306818181818</v>
+        <v>185.7878787878788</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>67.11363636363636</v>
+        <v>67.20202020202019</v>
       </c>
       <c r="T3" t="n">
-        <v>1198721.590909091</v>
+        <v>1204545.454545454</v>
       </c>
       <c r="U3" t="n">
-        <v>69.70454545454545</v>
+        <v>69.61616161616161</v>
       </c>
       <c r="V3" t="n">
-        <v>25.88363636363636</v>
+        <v>25.59848484848484</v>
       </c>
       <c r="W3" t="n">
-        <v>183.4181818181818</v>
+        <v>182.9924242424242</v>
       </c>
       <c r="X3" t="n">
-        <v>1.592727272727272</v>
+        <v>1.568181818181818</v>
       </c>
       <c r="Y3" t="n">
-        <v>74.4290909090909</v>
+        <v>74.40151515151514</v>
       </c>
       <c r="Z3" t="n">
-        <v>6750181.818181817</v>
+        <v>6821969.696969698</v>
       </c>
       <c r="AA3" t="n">
-        <v>78.27272727272728</v>
+        <v>78.58333333333333</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.62760416666667</v>
+        <v>24.32561728395062</v>
       </c>
       <c r="AC3" t="n">
-        <v>184.0234375</v>
+        <v>183.5354938271605</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>64.81336805555554</v>
+        <v>64.92746913580247</v>
       </c>
       <c r="AF3" t="n">
-        <v>966861.9791666667</v>
+        <v>1005285.49382716</v>
       </c>
       <c r="AG3" t="n">
-        <v>68.68923611111111</v>
+        <v>69.12654320987654</v>
       </c>
       <c r="AH3" t="n">
-        <v>26.10392546583851</v>
+        <v>26.39302248677249</v>
       </c>
       <c r="AI3" t="n">
-        <v>184.7884375431332</v>
+        <v>185.5456349206349</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.496536231884058</v>
+        <v>1.517526455026455</v>
       </c>
       <c r="AK3" t="n">
-        <v>72.19923188405797</v>
+        <v>72.56084656084656</v>
       </c>
       <c r="AL3" t="n">
-        <v>4507439.320220841</v>
+        <v>4633196.924603174</v>
       </c>
       <c r="AM3" t="n">
-        <v>76.34969082125603</v>
+        <v>76.51157407407408</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>26.43181818181818</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>185.7916666666667</v>
+        <v>185.6363636363637</v>
       </c>
       <c r="X4" t="n">
-        <v>1.78030303030303</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="Y4" t="n">
-        <v>75.21590909090908</v>
+        <v>75.33333333333334</v>
       </c>
       <c r="Z4" t="n">
-        <v>8631818.181818182</v>
+        <v>8990909.090909092</v>
       </c>
       <c r="AA4" t="n">
-        <v>78.88257575757576</v>
+        <v>78.75757575757575</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -993,22 +993,22 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>24.32393389118932</v>
+        <v>24.380291005291</v>
       </c>
       <c r="AI4" t="n">
-        <v>184.7463804060272</v>
+        <v>185.2876984126984</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.346938262019783</v>
+        <v>1.371858465608465</v>
       </c>
       <c r="AK4" t="n">
-        <v>70.98909449045318</v>
+        <v>71.54580026455027</v>
       </c>
       <c r="AL4" t="n">
-        <v>4994844.414970095</v>
+        <v>5163723.544973545</v>
       </c>
       <c r="AM4" t="n">
-        <v>77.42874036691971</v>
+        <v>77.71660052910052</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr">
@@ -1082,22 +1082,22 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>27.18560606060606</v>
+        <v>27.17424242424243</v>
       </c>
       <c r="W5" t="n">
-        <v>185.1931818181818</v>
+        <v>184.9469696969697</v>
       </c>
       <c r="X5" t="n">
-        <v>3.143939393939394</v>
+        <v>3.015151515151516</v>
       </c>
       <c r="Y5" t="n">
-        <v>82.46969696969698</v>
+        <v>81.68939393939394</v>
       </c>
       <c r="Z5" t="n">
-        <v>45745265.15151515</v>
+        <v>39014393.93939394</v>
       </c>
       <c r="AA5" t="n">
-        <v>84.97727272727273</v>
+        <v>84.40151515151514</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1106,22 +1106,22 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>24.87941074758152</v>
+        <v>24.45712106352839</v>
       </c>
       <c r="AI5" t="n">
-        <v>182.0659746643728</v>
+        <v>182.0672128347328</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.147727117943079</v>
+        <v>2.167504152343969</v>
       </c>
       <c r="AK5" t="n">
-        <v>77.91587622678513</v>
+        <v>77.9537588584714</v>
       </c>
       <c r="AL5" t="n">
-        <v>26298143.27481081</v>
+        <v>27552763.46238964</v>
       </c>
       <c r="AM5" t="n">
-        <v>83.04825326725356</v>
+        <v>83.28191797978697</v>
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
@@ -1199,22 +1199,22 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>24.84925252525252</v>
+        <v>25.36186868686869</v>
       </c>
       <c r="W6" t="n">
-        <v>184.8076767676768</v>
+        <v>184.8122895622895</v>
       </c>
       <c r="X6" t="n">
-        <v>1.49220202020202</v>
+        <v>1.506902356902357</v>
       </c>
       <c r="Y6" t="n">
-        <v>75.25357575757576</v>
+        <v>75.14865319865319</v>
       </c>
       <c r="Z6" t="n">
-        <v>8616650.505050505</v>
+        <v>8163392.255892255</v>
       </c>
       <c r="AA6" t="n">
-        <v>78.27482828282828</v>
+        <v>78.04478114478115</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1223,22 +1223,22 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>23.43553056554429</v>
+        <v>22.77183947186808</v>
       </c>
       <c r="AI6" t="n">
-        <v>183.4115297482838</v>
+        <v>183.8194072136864</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.295255403000254</v>
+        <v>1.2656941266209</v>
       </c>
       <c r="AK6" t="n">
-        <v>72.71196026297628</v>
+        <v>72.58214274363445</v>
       </c>
       <c r="AL6" t="n">
-        <v>6241387.857324472</v>
+        <v>6659763.062547673</v>
       </c>
       <c r="AM6" t="n">
-        <v>78.22619705059751</v>
+        <v>78.87316184482945</v>
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
@@ -1309,22 +1309,22 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>23.73030303030303</v>
+        <v>23.81558441558441</v>
       </c>
       <c r="W7" t="n">
-        <v>183.2090909090909</v>
+        <v>183.0974025974026</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>69.14181818181818</v>
+        <v>68.95974025974024</v>
       </c>
       <c r="Z7" t="n">
-        <v>2332030.303030303</v>
+        <v>2284870.12987013</v>
       </c>
       <c r="AA7" t="n">
-        <v>75.36121212121212</v>
+        <v>75.07402597402597</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1333,22 +1333,22 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>22.88650793650794</v>
+        <v>22.53741496598639</v>
       </c>
       <c r="AI7" t="n">
-        <v>183.4554232804233</v>
+        <v>183.7338435374149</v>
       </c>
       <c r="AJ7" t="n">
         <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>63.91600529100528</v>
+        <v>63.16808390022675</v>
       </c>
       <c r="AL7" t="n">
-        <v>1211101.190476191</v>
+        <v>1147456.065759637</v>
       </c>
       <c r="AM7" t="n">
-        <v>71.86428571428571</v>
+        <v>72.031179138322</v>
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr">
@@ -1426,22 +1426,22 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>26.28</v>
+        <v>25.81428571428571</v>
       </c>
       <c r="W8" t="n">
-        <v>185.8266666666667</v>
+        <v>186.4857142857143</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>69.52666666666667</v>
+        <v>68.95714285714287</v>
       </c>
       <c r="Z8" t="n">
-        <v>1836666.666666667</v>
+        <v>1752500</v>
       </c>
       <c r="AA8" t="n">
-        <v>73.32666666666667</v>
+        <v>73.78571428571429</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1450,22 +1450,22 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>25.59672364672365</v>
+        <v>24.8501221001221</v>
       </c>
       <c r="AI8" t="n">
-        <v>185.5155270655271</v>
+        <v>184.8923992673993</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.075925925925926</v>
+        <v>1.033730158730159</v>
       </c>
       <c r="AK8" t="n">
-        <v>67.41816239316239</v>
+        <v>66.65201465201464</v>
       </c>
       <c r="AL8" t="n">
-        <v>1430449.786324786</v>
+        <v>1401608.669108669</v>
       </c>
       <c r="AM8" t="n">
-        <v>72.78931623931622</v>
+        <v>72.44337606837607</v>
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr">
@@ -1539,22 +1539,22 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>27.01090909090909</v>
+        <v>26.92424242424242</v>
       </c>
       <c r="W9" t="n">
-        <v>184.9454545454546</v>
+        <v>184.7045454545455</v>
       </c>
       <c r="X9" t="n">
-        <v>1.629090909090909</v>
+        <v>1.606060606060606</v>
       </c>
       <c r="Y9" t="n">
-        <v>75.80727272727273</v>
+        <v>75.81060606060606</v>
       </c>
       <c r="Z9" t="n">
-        <v>8416181.818181818</v>
+        <v>8463636.363636365</v>
       </c>
       <c r="AA9" t="n">
-        <v>78.08000000000001</v>
+        <v>78.24242424242425</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
@@ -1563,22 +1563,22 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>26.84057934691802</v>
+        <v>26.95259586163476</v>
       </c>
       <c r="AI9" t="n">
-        <v>183.9944046710981</v>
+        <v>184.4976023240469</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.480745523228361</v>
+        <v>1.469145765985011</v>
       </c>
       <c r="AK9" t="n">
-        <v>73.74021230612765</v>
+        <v>73.88470156369185</v>
       </c>
       <c r="AL9" t="n">
-        <v>5214261.759471141</v>
+        <v>5168253.665564879</v>
       </c>
       <c r="AM9" t="n">
-        <v>76.13055464748828</v>
+        <v>76.10069255263764</v>
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr">
@@ -1652,22 +1652,22 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>25.32299465240642</v>
+        <v>25.39886363636364</v>
       </c>
       <c r="W10" t="n">
-        <v>183.8994652406417</v>
+        <v>183.7329545454546</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>68.35828877005349</v>
+        <v>68.33522727272728</v>
       </c>
       <c r="Z10" t="n">
-        <v>1690708.556149733</v>
+        <v>1673380.681818182</v>
       </c>
       <c r="AA10" t="n">
-        <v>71.55080213903743</v>
+        <v>71.47499999999999</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
@@ -1676,22 +1676,22 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>26.18457831783986</v>
+        <v>26.49465948096526</v>
       </c>
       <c r="AI10" t="n">
-        <v>182.0612779089863</v>
+        <v>181.2934100010402</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>67.48334383680663</v>
+        <v>67.60523065321406</v>
       </c>
       <c r="AL10" t="n">
-        <v>1437494.328464345</v>
+        <v>1398703.22576451</v>
       </c>
       <c r="AM10" t="n">
-        <v>70.6244564707514</v>
+        <v>70.25405333368005</v>
       </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr">
@@ -1769,22 +1769,22 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>25.01515151515152</v>
+        <v>24.65909090909091</v>
       </c>
       <c r="W11" t="n">
-        <v>182.7034090909091</v>
+        <v>182.8272727272727</v>
       </c>
       <c r="X11" t="n">
-        <v>2.114772727272727</v>
+        <v>2.075757575757576</v>
       </c>
       <c r="Y11" t="n">
-        <v>80.2594696969697</v>
+        <v>80.28181818181818</v>
       </c>
       <c r="Z11" t="n">
-        <v>28676704.54545455</v>
+        <v>29237121.21212121</v>
       </c>
       <c r="AA11" t="n">
-        <v>83.63409090909092</v>
+        <v>83.88939393939394</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1793,22 +1793,22 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>24.78276685070164</v>
+        <v>24.99997843340235</v>
       </c>
       <c r="AI11" t="n">
-        <v>185.307395905222</v>
+        <v>184.8588106740281</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.666533672647803</v>
+        <v>1.721043248217162</v>
       </c>
       <c r="AK11" t="n">
-        <v>76.70394453071084</v>
+        <v>76.84006211180125</v>
       </c>
       <c r="AL11" t="n">
-        <v>17697117.9836669</v>
+        <v>17745793.79457097</v>
       </c>
       <c r="AM11" t="n">
-        <v>81.43627070393374</v>
+        <v>81.4256599378882</v>
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr">
@@ -1880,76 +1880,76 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>25.55090909090909</v>
+        <v>25.6987012987013</v>
       </c>
       <c r="Q12" t="n">
-        <v>183.4945454545455</v>
+        <v>183.5805194805195</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>67.17090909090909</v>
+        <v>66.98181818181818</v>
       </c>
       <c r="T12" t="n">
-        <v>1433590.909090909</v>
+        <v>1359707.792207792</v>
       </c>
       <c r="U12" t="n">
-        <v>71.06242424242424</v>
+        <v>70.96493506493506</v>
       </c>
       <c r="V12" t="n">
-        <v>27.23484848484849</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="W12" t="n">
-        <v>183.7840909090909</v>
+        <v>183.5681818181818</v>
       </c>
       <c r="X12" t="n">
-        <v>1.712121212121212</v>
+        <v>1.696969696969697</v>
       </c>
       <c r="Y12" t="n">
-        <v>75.54924242424242</v>
+        <v>75.43939393939394</v>
       </c>
       <c r="Z12" t="n">
-        <v>9118181.818181818</v>
+        <v>8703787.878787877</v>
       </c>
       <c r="AA12" t="n">
-        <v>77.40151515151516</v>
+        <v>77.17424242424242</v>
       </c>
       <c r="AB12" t="n">
-        <v>26.20886243386243</v>
+        <v>25.67375283446712</v>
       </c>
       <c r="AC12" t="n">
-        <v>185.1949735449735</v>
+        <v>184.3086734693877</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>66.5681216931217</v>
+        <v>66.60827664399093</v>
       </c>
       <c r="AF12" t="n">
-        <v>1171283.068783069</v>
+        <v>1250368.480725624</v>
       </c>
       <c r="AG12" t="n">
-        <v>69.75132275132275</v>
+        <v>69.77069160997732</v>
       </c>
       <c r="AH12" t="n">
-        <v>24.99484444807672</v>
+        <v>24.72535573535288</v>
       </c>
       <c r="AI12" t="n">
-        <v>184.9159408560653</v>
+        <v>184.9018840125676</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.470589479435303</v>
+        <v>1.432053412516799</v>
       </c>
       <c r="AK12" t="n">
-        <v>73.55038975003936</v>
+        <v>73.17647538229632</v>
       </c>
       <c r="AL12" t="n">
-        <v>6272273.95367949</v>
+        <v>5758952.669263739</v>
       </c>
       <c r="AM12" t="n">
-        <v>76.75503260339859</v>
+        <v>76.68100924866513</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -2027,22 +2027,22 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>25.90909090909091</v>
+        <v>25.64393939393939</v>
       </c>
       <c r="W13" t="n">
-        <v>186.6600790513834</v>
+        <v>186.6818181818182</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>72.84584980237155</v>
+        <v>72.91666666666667</v>
       </c>
       <c r="Z13" t="n">
-        <v>4341600.790513834</v>
+        <v>4475189.393939394</v>
       </c>
       <c r="AA13" t="n">
-        <v>75.09090909090909</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -2051,22 +2051,22 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>27.13732109100729</v>
+        <v>27.22056878306878</v>
       </c>
       <c r="AI13" t="n">
-        <v>182.9290665226393</v>
+        <v>183.088458994709</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>69.29181669517209</v>
+        <v>69.15658068783068</v>
       </c>
       <c r="AL13" t="n">
-        <v>1847953.329882677</v>
+        <v>1897767.857142857</v>
       </c>
       <c r="AM13" t="n">
-        <v>71.04263059981396</v>
+        <v>70.8599537037037</v>
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr">
@@ -2144,22 +2144,22 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>25.11688311688312</v>
+        <v>25.24675324675325</v>
       </c>
       <c r="W14" t="n">
-        <v>186.1233766233766</v>
+        <v>186.4545454545454</v>
       </c>
       <c r="X14" t="n">
         <v>1.077922077922078</v>
       </c>
       <c r="Y14" t="n">
-        <v>68.64935064935064</v>
+        <v>68.55844155844156</v>
       </c>
       <c r="Z14" t="n">
-        <v>1789935.064935065</v>
+        <v>1760389.610389611</v>
       </c>
       <c r="AA14" t="n">
-        <v>72.63636363636364</v>
+        <v>72.53246753246754</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -2168,22 +2168,22 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>24.93359336488218</v>
+        <v>25.11718672976437</v>
       </c>
       <c r="AI14" t="n">
-        <v>186.3180210489993</v>
+        <v>186.0427881297447</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.006506950606329</v>
+        <v>1.013013901212659</v>
       </c>
       <c r="AK14" t="n">
-        <v>66.12969535640343</v>
+        <v>66.52923198264814</v>
       </c>
       <c r="AL14" t="n">
-        <v>1283584.892290249</v>
+        <v>1377735.260770975</v>
       </c>
       <c r="AM14" t="n">
-        <v>70.97450828157351</v>
+        <v>71.19108005521049</v>
       </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr">
@@ -2261,22 +2261,22 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>25.90909090909091</v>
+        <v>25.72727272727272</v>
       </c>
       <c r="W15" t="n">
-        <v>183.6121212121212</v>
+        <v>183.6233766233766</v>
       </c>
       <c r="X15" t="n">
-        <v>1.16969696969697</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="Y15" t="n">
-        <v>69.7818181818182</v>
+        <v>69.63636363636364</v>
       </c>
       <c r="Z15" t="n">
-        <v>2006363.636363636</v>
+        <v>2008441.558441559</v>
       </c>
       <c r="AA15" t="n">
-        <v>73.73333333333333</v>
+        <v>73.83116883116882</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2285,22 +2285,22 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>24.07195767195767</v>
+        <v>24.08078231292517</v>
       </c>
       <c r="AI15" t="n">
-        <v>184.3002645502646</v>
+        <v>183.9410430839002</v>
       </c>
       <c r="AJ15" t="n">
         <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>66.04722222222222</v>
+        <v>66.1686507936508</v>
       </c>
       <c r="AL15" t="n">
-        <v>1300539.021164021</v>
+        <v>1337414.965986395</v>
       </c>
       <c r="AM15" t="n">
-        <v>71.710582010582</v>
+        <v>71.44727891156462</v>
       </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr">
@@ -2378,22 +2378,22 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>25.8300395256917</v>
+        <v>25.3030303030303</v>
       </c>
       <c r="W16" t="n">
-        <v>184.4901185770751</v>
+        <v>184.6363636363636</v>
       </c>
       <c r="X16" t="n">
-        <v>2.33201581027668</v>
+        <v>2.295454545454545</v>
       </c>
       <c r="Y16" t="n">
-        <v>80.31225296442688</v>
+        <v>79.88636363636364</v>
       </c>
       <c r="Z16" t="n">
-        <v>29751383.39920948</v>
+        <v>29481060.60606061</v>
       </c>
       <c r="AA16" t="n">
-        <v>83.15415019762845</v>
+        <v>83.25757575757576</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2402,22 +2402,22 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>24.84385783298827</v>
+        <v>25.150958994709</v>
       </c>
       <c r="AI16" t="n">
-        <v>183.8487750172533</v>
+        <v>183.9763558201058</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.962215320910973</v>
+        <v>2.013227513227513</v>
       </c>
       <c r="AK16" t="n">
-        <v>77.3852657004831</v>
+        <v>77.81018518518518</v>
       </c>
       <c r="AL16" t="n">
-        <v>18611827.12215321</v>
+        <v>20326719.57671958</v>
       </c>
       <c r="AM16" t="n">
-        <v>82.16485507246377</v>
+        <v>82.11458333333333</v>
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr">
@@ -2495,22 +2495,22 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>23.75151515151515</v>
+        <v>23.4025974025974</v>
       </c>
       <c r="W17" t="n">
-        <v>183.9030303030303</v>
+        <v>183.3506493506493</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>67.47272727272727</v>
+        <v>67.16883116883118</v>
       </c>
       <c r="Z17" t="n">
-        <v>1659090.909090909</v>
+        <v>1636688.311688312</v>
       </c>
       <c r="AA17" t="n">
-        <v>73.03636363636363</v>
+        <v>73.16883116883116</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2519,28 +2519,24 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>26.40824915824916</v>
+        <v>27.22204184704185</v>
       </c>
       <c r="AI17" t="n">
-        <v>183.167760942761</v>
+        <v>182.7880591630591</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>66.72912457912459</v>
+        <v>67.27272727272728</v>
       </c>
       <c r="AL17" t="n">
-        <v>1104993.686868687</v>
+        <v>1142446.789321789</v>
       </c>
       <c r="AM17" t="n">
-        <v>69.79309764309764</v>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>trS1MB7T</t>
-        </is>
-      </c>
+        <v>69.34433621933621</v>
+      </c>
+      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
           <t>YmfcAeCo</t>
@@ -2605,22 +2601,22 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>25.65046296296296</v>
+        <v>25.36296296296297</v>
       </c>
       <c r="W18" t="n">
-        <v>185.8619107744108</v>
+        <v>185.9469696969697</v>
       </c>
       <c r="X18" t="n">
-        <v>1.45976430976431</v>
+        <v>1.440824915824916</v>
       </c>
       <c r="Y18" t="n">
-        <v>74.625</v>
+        <v>74.36851851851851</v>
       </c>
       <c r="Z18" t="n">
-        <v>6710662.878787879</v>
+        <v>6684659.090909091</v>
       </c>
       <c r="AA18" t="n">
-        <v>77.19234006734007</v>
+        <v>77.4013468013468</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2629,22 +2625,22 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>24.30819129718607</v>
+        <v>23.83559237424369</v>
       </c>
       <c r="AI18" t="n">
-        <v>183.6187468960205</v>
+        <v>184.5199887344624</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.147585874129024</v>
+        <v>1.132095785549733</v>
       </c>
       <c r="AK18" t="n">
-        <v>71.62761588453829</v>
+        <v>70.95658440609098</v>
       </c>
       <c r="AL18" t="n">
-        <v>4006952.868060768</v>
+        <v>3835458.293381813</v>
       </c>
       <c r="AM18" t="n">
-        <v>76.39876906736912</v>
+        <v>76.48222109883294</v>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
@@ -2711,22 +2707,22 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>24.03515151515152</v>
+        <v>23.94545454545455</v>
       </c>
       <c r="W19" t="n">
-        <v>185.7927272727273</v>
+        <v>185.6987012987013</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>66.72363636363637</v>
+        <v>66.48571428571429</v>
       </c>
       <c r="Z19" t="n">
-        <v>1459409.090909091</v>
+        <v>1437370.12987013</v>
       </c>
       <c r="AA19" t="n">
-        <v>72.31393939393939</v>
+        <v>72.51688311688312</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2735,22 +2731,22 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>24.71506263462785</v>
+        <v>25.11362628055175</v>
       </c>
       <c r="AI19" t="n">
-        <v>185.7294984001506</v>
+        <v>186.4101496329757</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>66.6373611895351</v>
+        <v>67.01883520206501</v>
       </c>
       <c r="AL19" t="n">
-        <v>1347724.371039589</v>
+        <v>1372780.96515286</v>
       </c>
       <c r="AM19" t="n">
-        <v>71.76849342284125</v>
+        <v>71.23804146164395</v>
       </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr">
@@ -2822,76 +2818,76 @@
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>26.54969696969697</v>
+        <v>26.55844155844155</v>
       </c>
       <c r="Q20" t="n">
-        <v>184.3387878787879</v>
+        <v>183.7662337662337</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>67.76242424242425</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="T20" t="n">
-        <v>1327106.060606061</v>
+        <v>1327922.077922078</v>
       </c>
       <c r="U20" t="n">
-        <v>70.56363636363636</v>
+        <v>70.49350649350649</v>
       </c>
       <c r="V20" t="n">
-        <v>24.13515151515151</v>
+        <v>24.14285714285714</v>
       </c>
       <c r="W20" t="n">
-        <v>184.7472727272728</v>
+        <v>184.6714285714286</v>
       </c>
       <c r="X20" t="n">
-        <v>1.066666666666667</v>
+        <v>1.071428571428572</v>
       </c>
       <c r="Y20" t="n">
-        <v>70.52060606060606</v>
+        <v>70.58571428571429</v>
       </c>
       <c r="Z20" t="n">
-        <v>2836121.212121212</v>
+        <v>2848571.428571429</v>
       </c>
       <c r="AA20" t="n">
-        <v>75.59393939393939</v>
+        <v>75.45714285714287</v>
       </c>
       <c r="AB20" t="n">
-        <v>24.73087761674718</v>
+        <v>25.16707335107956</v>
       </c>
       <c r="AC20" t="n">
-        <v>183.3894007361399</v>
+        <v>183.6615276545401</v>
       </c>
       <c r="AD20" t="n">
         <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>66.39468599033816</v>
+        <v>66.62325002464753</v>
       </c>
       <c r="AF20" t="n">
-        <v>1208483.868184955</v>
+        <v>1202547.631371389</v>
       </c>
       <c r="AG20" t="n">
-        <v>70.55429031515989</v>
+        <v>70.29122301094351</v>
       </c>
       <c r="AH20" t="n">
-        <v>25.90440594239221</v>
+        <v>25.75887441170213</v>
       </c>
       <c r="AI20" t="n">
-        <v>183.115808845786</v>
+        <v>183.161994011945</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.214467630428729</v>
+        <v>1.230265103753172</v>
       </c>
       <c r="AK20" t="n">
-        <v>68.62940200743405</v>
+        <v>68.67751677329971</v>
       </c>
       <c r="AL20" t="n">
-        <v>1668354.536704079</v>
+        <v>1714543.735114183</v>
       </c>
       <c r="AM20" t="n">
-        <v>73.29311079631447</v>
+        <v>73.62469320298676</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -2969,22 +2965,22 @@
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>25.08484848484848</v>
+        <v>25.2987012987013</v>
       </c>
       <c r="W21" t="n">
-        <v>182.4909090909091</v>
+        <v>182.1038961038961</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>67.2909090909091</v>
+        <v>67.24675324675324</v>
       </c>
       <c r="Z21" t="n">
-        <v>1338393.93939394</v>
+        <v>1323831.168831169</v>
       </c>
       <c r="AA21" t="n">
-        <v>70.96969696969697</v>
+        <v>70.93506493506494</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2993,22 +2989,22 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="n">
-        <v>27.9031746031746</v>
+        <v>27.87244897959183</v>
       </c>
       <c r="AI21" t="n">
-        <v>181.1016471734893</v>
+        <v>180.7478607232367</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>64.24054859370649</v>
+        <v>64.68581274615109</v>
       </c>
       <c r="AL21" t="n">
-        <v>731285.8047897521</v>
+        <v>767403.8220551378</v>
       </c>
       <c r="AM21" t="n">
-        <v>65.70394458368143</v>
+        <v>66.2298245614035</v>
       </c>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr">
@@ -3086,22 +3082,22 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>27.92777777777778</v>
+        <v>27.8968253968254</v>
       </c>
       <c r="W22" t="n">
-        <v>183.1965811965812</v>
+        <v>182.5682539682539</v>
       </c>
       <c r="X22" t="n">
-        <v>1.265811965811966</v>
+        <v>1.253174603174603</v>
       </c>
       <c r="Y22" t="n">
-        <v>73.1794871794872</v>
+        <v>73.20793650793651</v>
       </c>
       <c r="Z22" t="n">
-        <v>3630032.051282051</v>
+        <v>3635853.174603175</v>
       </c>
       <c r="AA22" t="n">
-        <v>75.15897435897435</v>
+        <v>75.08888888888889</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
@@ -3110,22 +3106,22 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>26.73745421245421</v>
+        <v>26.92941930395347</v>
       </c>
       <c r="AI22" t="n">
-        <v>182.4158289460349</v>
+        <v>182.6555353304209</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.04545714900406</v>
+        <v>1.075362448564475</v>
       </c>
       <c r="AK22" t="n">
-        <v>70.09494745973578</v>
+        <v>70.67002245874427</v>
       </c>
       <c r="AL22" t="n">
-        <v>2184121.574697233</v>
+        <v>2429647.014204059</v>
       </c>
       <c r="AM22" t="n">
-        <v>73.0017850665734</v>
+        <v>73.44407969033257</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -3207,22 +3203,22 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>24.37878787878788</v>
+        <v>24.46969696969697</v>
       </c>
       <c r="W23" t="n">
-        <v>185.1439393939394</v>
+        <v>184.9924242424242</v>
       </c>
       <c r="X23" t="n">
-        <v>1.295454545454546</v>
+        <v>1.340909090909091</v>
       </c>
       <c r="Y23" t="n">
-        <v>72.5719696969697</v>
+        <v>72.67424242424242</v>
       </c>
       <c r="Z23" t="n">
-        <v>5912878.787878788</v>
+        <v>6025757.575757575</v>
       </c>
       <c r="AA23" t="n">
-        <v>77.85606060606061</v>
+        <v>77.86363636363636</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
@@ -3231,22 +3227,22 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>25.79629629629629</v>
+        <v>25.85069444444445</v>
       </c>
       <c r="AI23" t="n">
-        <v>185.338210978836</v>
+        <v>184.9386574074074</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.261739417989418</v>
+        <v>1.31712962962963</v>
       </c>
       <c r="AK23" t="n">
-        <v>69.37003968253968</v>
+        <v>69.62847222222223</v>
       </c>
       <c r="AL23" t="n">
-        <v>2715412.533068783</v>
+        <v>2937488.425925925</v>
       </c>
       <c r="AM23" t="n">
-        <v>74.37838955026454</v>
+        <v>74.60995370370371</v>
       </c>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr">
@@ -3317,22 +3313,22 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>26.21919191919192</v>
+        <v>25.8030303030303</v>
       </c>
       <c r="W24" t="n">
-        <v>185.9505892255892</v>
+        <v>186.569696969697</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>70.73985690235691</v>
+        <v>70.64848484848484</v>
       </c>
       <c r="Z24" t="n">
-        <v>2382124.368686868</v>
+        <v>2422405.303030303</v>
       </c>
       <c r="AA24" t="n">
-        <v>73.69482323232323</v>
+        <v>74.09242424242423</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
@@ -3341,22 +3337,22 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>26.09022927407678</v>
+        <v>26.23151387366541</v>
       </c>
       <c r="AI24" t="n">
-        <v>187.1591262652404</v>
+        <v>186.5838739360479</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>68.58049072890026</v>
+        <v>68.65077326824449</v>
       </c>
       <c r="AL24" t="n">
-        <v>1616511.003404985</v>
+        <v>1616994.789763732</v>
       </c>
       <c r="AM24" t="n">
-        <v>71.57790316005629</v>
+        <v>71.31078389085103</v>
       </c>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr">
@@ -3434,22 +3430,22 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>26.92857142857143</v>
+        <v>26.66233766233767</v>
       </c>
       <c r="W25" t="n">
-        <v>183.7207792207792</v>
+        <v>183.4935064935065</v>
       </c>
       <c r="X25" t="n">
-        <v>1.012987012987013</v>
+        <v>1.025974025974026</v>
       </c>
       <c r="Y25" t="n">
-        <v>68.8896103896104</v>
+        <v>68.6883116883117</v>
       </c>
       <c r="Z25" t="n">
-        <v>1643506.493506493</v>
+        <v>1667532.467532468</v>
       </c>
       <c r="AA25" t="n">
-        <v>72.82467532467531</v>
+        <v>72.98701298701299</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -3458,22 +3454,22 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="n">
-        <v>26.57823129251701</v>
+        <v>27.28344671201814</v>
       </c>
       <c r="AI25" t="n">
-        <v>182.9632936507936</v>
+        <v>182.563492063492</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.127551020408163</v>
+        <v>1.219387755102041</v>
       </c>
       <c r="AK25" t="n">
-        <v>66.68168934240363</v>
+        <v>67.30187074829932</v>
       </c>
       <c r="AL25" t="n">
-        <v>1140865.929705215</v>
+        <v>1239321.145124716</v>
       </c>
       <c r="AM25" t="n">
-        <v>71.36096938775509</v>
+        <v>71.34495464852607</v>
       </c>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr">
@@ -3551,22 +3547,22 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>24.6569696969697</v>
+        <v>24.61558441558442</v>
       </c>
       <c r="W26" t="n">
-        <v>183.4224242424243</v>
+        <v>183.074025974026</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>70.77696969696969</v>
+        <v>70.61298701298701</v>
       </c>
       <c r="Z26" t="n">
-        <v>2776363.636363636</v>
+        <v>2690909.090909091</v>
       </c>
       <c r="AA26" t="n">
-        <v>74.53636363636363</v>
+        <v>74.3831168831169</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
@@ -3575,22 +3571,22 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="n">
-        <v>25.16001683501684</v>
+        <v>25.27146464646465</v>
       </c>
       <c r="AI26" t="n">
-        <v>181.9852212602213</v>
+        <v>181.5678210678211</v>
       </c>
       <c r="AJ26" t="n">
         <v>1</v>
       </c>
       <c r="AK26" t="n">
-        <v>69.51005291005292</v>
+        <v>70.17460317460318</v>
       </c>
       <c r="AL26" t="n">
-        <v>2252022.607022607</v>
+        <v>2475252.525252525</v>
       </c>
       <c r="AM26" t="n">
-        <v>73.00972823472824</v>
+        <v>73.31421356421356</v>
       </c>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr">
@@ -3668,22 +3664,22 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>25.11111111111111</v>
+        <v>25.31313131313131</v>
       </c>
       <c r="W27" t="n">
-        <v>184.4848484848485</v>
+        <v>184.6868686868687</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>70.1919191919192</v>
+        <v>70.50505050505051</v>
       </c>
       <c r="Z27" t="n">
-        <v>2569696.96969697</v>
+        <v>2639646.464646464</v>
       </c>
       <c r="AA27" t="n">
-        <v>74.17676767676767</v>
+        <v>74.05050505050505</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
@@ -3692,22 +3688,22 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>23.50694444444444</v>
+        <v>24.04938271604938</v>
       </c>
       <c r="AI27" t="n">
-        <v>186.0601851851852</v>
+        <v>185.7808641975309</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>66.11882716049382</v>
+        <v>67.11111111111111</v>
       </c>
       <c r="AL27" t="n">
-        <v>1558275.462962963</v>
+        <v>1687337.962962963</v>
       </c>
       <c r="AM27" t="n">
-        <v>72.07793209876543</v>
+        <v>72.63117283950618</v>
       </c>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr">
@@ -3785,22 +3781,22 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>26.06363636363636</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="W28" t="n">
-        <v>183.7435606060606</v>
+        <v>183.030303030303</v>
       </c>
       <c r="X28" t="n">
-        <v>1.147348484848485</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="Y28" t="n">
-        <v>73.18333333333334</v>
+        <v>73.31818181818181</v>
       </c>
       <c r="Z28" t="n">
-        <v>4895804.924242425</v>
+        <v>4940530.303030304</v>
       </c>
       <c r="AA28" t="n">
-        <v>76.06325757575758</v>
+        <v>76.03030303030303</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
@@ -3809,22 +3805,22 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>25.19132267943409</v>
+        <v>24.85555052334944</v>
       </c>
       <c r="AI28" t="n">
-        <v>184.7709140188939</v>
+        <v>184.9186611985882</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.259079632202487</v>
+        <v>1.13635859727822</v>
       </c>
       <c r="AK28" t="n">
-        <v>69.18188095540785</v>
+        <v>68.48530406632523</v>
       </c>
       <c r="AL28" t="n">
-        <v>2794284.061792464</v>
+        <v>2511872.270122771</v>
       </c>
       <c r="AM28" t="n">
-        <v>74.31118405918177</v>
+        <v>73.9932057650164</v>
       </c>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr">
@@ -3898,22 +3894,22 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>25.62857142857143</v>
+        <v>25.52857142857143</v>
       </c>
       <c r="W29" t="n">
-        <v>181.3642857142857</v>
+        <v>181.3142857142857</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>68.15000000000001</v>
+        <v>68.24285714285713</v>
       </c>
       <c r="Z29" t="n">
-        <v>1409642.857142857</v>
+        <v>1449285.714285714</v>
       </c>
       <c r="AA29" t="n">
-        <v>70.42857142857143</v>
+        <v>70.65714285714286</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
@@ -3922,22 +3918,22 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
-        <v>23.17202380952381</v>
+        <v>22.80436507936508</v>
       </c>
       <c r="AI29" t="n">
-        <v>181.225</v>
+        <v>180.4956349206349</v>
       </c>
       <c r="AJ29" t="n">
         <v>1</v>
       </c>
       <c r="AK29" t="n">
-        <v>65.63670634920635</v>
+        <v>65.29126984126984</v>
       </c>
       <c r="AL29" t="n">
-        <v>1277291.666666667</v>
+        <v>1244017.857142857</v>
       </c>
       <c r="AM29" t="n">
-        <v>70.6875</v>
+        <v>70.66071428571429</v>
       </c>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr">
@@ -4015,22 +4011,22 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>25.55189393939394</v>
+        <v>25.31666666666667</v>
       </c>
       <c r="W30" t="n">
-        <v>186.2450757575758</v>
+        <v>186.7</v>
       </c>
       <c r="X30" t="n">
-        <v>1.571212121212121</v>
+        <v>1.566666666666666</v>
       </c>
       <c r="Y30" t="n">
-        <v>75.99659090909091</v>
+        <v>75.875</v>
       </c>
       <c r="Z30" t="n">
-        <v>11083863.63636363</v>
+        <v>10947500</v>
       </c>
       <c r="AA30" t="n">
-        <v>79.62916666666666</v>
+        <v>79.58333333333333</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
@@ -4039,22 +4035,22 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>24.28577898550725</v>
+        <v>24.36808574879227</v>
       </c>
       <c r="AI30" t="n">
-        <v>184.1685185185185</v>
+        <v>183.4844907407407</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.25829307568438</v>
+        <v>1.255012077294686</v>
       </c>
       <c r="AK30" t="n">
-        <v>73.47984601449275</v>
+        <v>73.56385869565217</v>
       </c>
       <c r="AL30" t="n">
-        <v>8048716.787439614</v>
+        <v>8261773.852657005</v>
       </c>
       <c r="AM30" t="n">
-        <v>78.17277576489532</v>
+        <v>78.34231078904992</v>
       </c>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr">
@@ -4130,76 +4126,76 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>25.69090909090909</v>
+        <v>25.48051948051948</v>
       </c>
       <c r="Q31" t="n">
-        <v>184.7757575757575</v>
+        <v>184.5584415584416</v>
       </c>
       <c r="R31" t="n">
-        <v>1.078787878787879</v>
+        <v>1.064935064935065</v>
       </c>
       <c r="S31" t="n">
-        <v>67.53333333333333</v>
+        <v>67.40259740259741</v>
       </c>
       <c r="T31" t="n">
-        <v>1416060.606060606</v>
+        <v>1417207.792207792</v>
       </c>
       <c r="U31" t="n">
-        <v>71.06666666666666</v>
+        <v>71.09090909090909</v>
       </c>
       <c r="V31" t="n">
-        <v>24.2054292929293</v>
+        <v>24.17314814814815</v>
       </c>
       <c r="W31" t="n">
-        <v>183.2920454545455</v>
+        <v>183.1722222222222</v>
       </c>
       <c r="X31" t="n">
-        <v>1.674200336700337</v>
+        <v>1.65462962962963</v>
       </c>
       <c r="Y31" t="n">
-        <v>76.81498316498316</v>
+        <v>76.78055555555555</v>
       </c>
       <c r="Z31" t="n">
-        <v>15183578.49326599</v>
+        <v>15412175.92592593</v>
       </c>
       <c r="AA31" t="n">
-        <v>81.11140572390572</v>
+        <v>81.16944444444444</v>
       </c>
       <c r="AB31" t="n">
-        <v>26.2462962962963</v>
+        <v>26.19444444444444</v>
       </c>
       <c r="AC31" t="n">
-        <v>183.4342592592592</v>
+        <v>182.3432539682539</v>
       </c>
       <c r="AD31" t="n">
         <v>1</v>
       </c>
       <c r="AE31" t="n">
-        <v>66.59722222222223</v>
+        <v>66.7876984126984</v>
       </c>
       <c r="AF31" t="n">
-        <v>1237689.814814815</v>
+        <v>1275128.968253969</v>
       </c>
       <c r="AG31" t="n">
-        <v>69.95</v>
+        <v>70.03571428571429</v>
       </c>
       <c r="AH31" t="n">
-        <v>24.90495228527349</v>
+        <v>24.15238522442469</v>
       </c>
       <c r="AI31" t="n">
-        <v>183.5869284349837</v>
+        <v>183.9373034859877</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.499156685534395</v>
+        <v>1.403607028935976</v>
       </c>
       <c r="AK31" t="n">
-        <v>72.18333902939166</v>
+        <v>71.64384256094782</v>
       </c>
       <c r="AL31" t="n">
-        <v>6228215.411430388</v>
+        <v>5468893.576270222</v>
       </c>
       <c r="AM31" t="n">
-        <v>78.08648685085412</v>
+        <v>78.40204346092503</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -4279,76 +4275,76 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>25.53430602319492</v>
+        <v>25.62494172494172</v>
       </c>
       <c r="Q32" t="n">
-        <v>184.4677141788253</v>
+        <v>185.2397047397047</v>
       </c>
       <c r="R32" t="n">
-        <v>2.169322858211747</v>
+        <v>2.02937062937063</v>
       </c>
       <c r="S32" t="n">
-        <v>81.66719042274597</v>
+        <v>81.18275058275057</v>
       </c>
       <c r="T32" t="n">
-        <v>37101945.37972316</v>
+        <v>32260644.91064491</v>
       </c>
       <c r="U32" t="n">
-        <v>84.42667414889638</v>
+        <v>84.09184149184148</v>
       </c>
       <c r="V32" t="n">
-        <v>24.39272727272727</v>
+        <v>24.37121212121212</v>
       </c>
       <c r="W32" t="n">
-        <v>184.7272727272727</v>
+        <v>184.6439393939394</v>
       </c>
       <c r="X32" t="n">
-        <v>1.534545454545454</v>
+        <v>1.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>76.11272727272728</v>
+        <v>76.06060606060606</v>
       </c>
       <c r="Z32" t="n">
-        <v>11664000</v>
+        <v>11783333.33333333</v>
       </c>
       <c r="AA32" t="n">
-        <v>79.00000000000001</v>
+        <v>79.18181818181817</v>
       </c>
       <c r="AB32" t="n">
-        <v>23.14342195458392</v>
+        <v>22.9557055263577</v>
       </c>
       <c r="AC32" t="n">
-        <v>182.3085980685746</v>
+        <v>181.5306546714155</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.597039333805161</v>
+        <v>1.768393924915664</v>
       </c>
       <c r="AE32" t="n">
-        <v>77.56414795711771</v>
+        <v>79.01045548654244</v>
       </c>
       <c r="AF32" t="n">
-        <v>27738496.98608804</v>
+        <v>35925979.835382</v>
       </c>
       <c r="AG32" t="n">
-        <v>83.48672153563776</v>
+        <v>84.46879443020747</v>
       </c>
       <c r="AH32" t="n">
-        <v>23.86049137336094</v>
+        <v>24.37645502645502</v>
       </c>
       <c r="AI32" t="n">
-        <v>182.7170835058661</v>
+        <v>182.4883597883598</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.253840579710145</v>
+        <v>1.278604497354497</v>
       </c>
       <c r="AK32" t="n">
-        <v>71.08787370600413</v>
+        <v>71.13700396825396</v>
       </c>
       <c r="AL32" t="n">
-        <v>5865789.216701174</v>
+        <v>5657118.882275132</v>
       </c>
       <c r="AM32" t="n">
-        <v>76.36166666666666</v>
+        <v>75.64880952380953</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
